--- a/INSTANCES/instances_xlsx/A_MTN_5/273FL_10A_4.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/273FL_10A_4.xlsx
@@ -8943,7 +8943,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -9011,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -9045,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
